--- a/data/raw/20260601_single_carbon_growth/Carbon_platemap_7.8_2.xlsx
+++ b/data/raw/20260601_single_carbon_growth/Carbon_platemap_7.8_2.xlsx
@@ -1,100 +1,134 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="4"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Taulukko1" sheetId="1" r:id="rId5"/>
+    <sheet name="Taulukko1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <extLst>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="21">
   <si>
-    <t>Plate 3</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>ANC403</t>
-  </si>
-  <si>
-    <t>EVO403</t>
-  </si>
-  <si>
-    <t>ANC1896</t>
-  </si>
-  <si>
-    <t>EVO1896</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>G</t>
-  </si>
-  <si>
-    <t>H</t>
-  </si>
-  <si>
-    <t>Medium/carbon source</t>
-  </si>
-  <si>
-    <t>M9MM with arginine</t>
-  </si>
-  <si>
-    <t>M9MM with cysteine</t>
-  </si>
-  <si>
-    <t>M9MM with D-mannitol</t>
-  </si>
-  <si>
-    <t>Plate 4</t>
-  </si>
-  <si>
-    <t>M9MM with lactic acid</t>
-  </si>
-  <si>
-    <t>M9MM with sodium acetate</t>
-  </si>
-  <si>
-    <t>blank</t>
+    <t xml:space="preserve">Plate 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANC403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVO403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANC1896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVO1896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medium/carbon source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M9MM with asparagine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M9MM with cysteine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M9MM with D-mannitol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plate 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M9MM with lactic acid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M9MM with sodium acetate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">blank</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="General"/>
+  </numFmts>
+  <fonts count="6">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -102,96 +136,191 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA4C2F4"/>
-        <bgColor rgb="FFA4C2F4"/>
+        <bgColor rgb="FFC0C0C0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9D2E9"/>
-        <bgColor rgb="FFD9D2E9"/>
+        <bgColor rgb="FFC0C0C0"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="4">
-    <border/>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
-    <border>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
     </border>
-    <border>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="11">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="6">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFD9D2E9"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FFA4C2F4"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -237,59 +366,55 @@
     </a:clrScheme>
     <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
                 <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
                 <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
                 <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
                 <a:lumMod val="102000"/>
                 <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
                 <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
               </a:schemeClr>
@@ -297,33 +422,24 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
                 <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
@@ -336,13 +452,7 @@
           <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -352,15 +462,13 @@
         <a:solidFill>
           <a:schemeClr val="phClr">
             <a:tint val="95000"/>
-            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
               </a:schemeClr>
@@ -368,7 +476,6 @@
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
               </a:schemeClr>
@@ -376,11 +483,11 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="63000"/>
-                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -389,56 +496,58 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <outlinePr summaryBelow="0"/>
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:O23"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1">
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
-      <c r="C1" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="D1" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="E1" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="F1" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="G1" s="3">
-        <v>5.0</v>
-      </c>
-      <c r="H1" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="I1" s="3">
-        <v>7.0</v>
-      </c>
-      <c r="J1" s="3">
-        <v>8.0</v>
-      </c>
-      <c r="K1" s="3">
-        <v>9.0</v>
-      </c>
-      <c r="L1" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="M1" s="3">
-        <v>11.0</v>
-      </c>
-      <c r="N1" s="3">
-        <v>12.0</v>
+      <c r="C1" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I1" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J1" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="K1" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="L1" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="M1" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="N1" s="3" t="n">
+        <v>12</v>
       </c>
       <c r="O1" s="2"/>
     </row>
-    <row r="2">
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
@@ -481,7 +590,7 @@
       </c>
       <c r="O2" s="2"/>
     </row>
-    <row r="3">
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2"/>
       <c r="B3" s="2" t="s">
         <v>6</v>
@@ -524,7 +633,7 @@
       </c>
       <c r="O3" s="2"/>
     </row>
-    <row r="4">
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2"/>
       <c r="B4" s="2" t="s">
         <v>7</v>
@@ -567,7 +676,7 @@
       </c>
       <c r="O4" s="2"/>
     </row>
-    <row r="5">
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2"/>
       <c r="B5" s="2" t="s">
         <v>8</v>
@@ -610,7 +719,7 @@
       </c>
       <c r="O5" s="2"/>
     </row>
-    <row r="6">
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
         <v>9</v>
@@ -653,7 +762,7 @@
       </c>
       <c r="O6" s="2"/>
     </row>
-    <row r="7">
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2"/>
       <c r="B7" s="2" t="s">
         <v>10</v>
@@ -696,7 +805,7 @@
       </c>
       <c r="O7" s="2"/>
     </row>
-    <row r="8">
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2"/>
       <c r="B8" s="2" t="s">
         <v>11</v>
@@ -739,7 +848,7 @@
       </c>
       <c r="O8" s="2"/>
     </row>
-    <row r="9">
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2"/>
       <c r="B9" s="2" t="s">
         <v>12</v>
@@ -782,7 +891,7 @@
       </c>
       <c r="O9" s="2"/>
     </row>
-    <row r="10">
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
         <v>13</v>
       </c>
@@ -790,32 +899,41 @@
       <c r="C10" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8" t="s">
         <v>15</v>
       </c>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
       <c r="K10" s="8" t="s">
         <v>16</v>
       </c>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
       <c r="O10" s="2"/>
     </row>
-    <row r="11">
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7"/>
       <c r="B11" s="2"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
-      <c r="N11" s="10"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="9"/>
       <c r="O11" s="2"/>
     </row>
-    <row r="12">
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -832,7 +950,7 @@
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
     </row>
-    <row r="13">
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -849,50 +967,50 @@
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
     </row>
-    <row r="14">
-      <c r="A14" s="11" t="s">
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="10" t="s">
         <v>17</v>
       </c>
       <c r="B14" s="2"/>
-      <c r="C14" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="D14" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>5.0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>7.0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>8.0</v>
-      </c>
-      <c r="K14" s="3">
-        <v>9.0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="M14" s="3">
-        <v>11.0</v>
-      </c>
-      <c r="N14" s="3">
-        <v>12.0</v>
+      <c r="C14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>12</v>
       </c>
       <c r="O14" s="2"/>
     </row>
-    <row r="15">
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2"/>
       <c r="B15" s="2" t="s">
         <v>1</v>
@@ -927,7 +1045,7 @@
       <c r="N15" s="5"/>
       <c r="O15" s="2"/>
     </row>
-    <row r="16">
+    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2"/>
       <c r="B16" s="2" t="s">
         <v>6</v>
@@ -962,7 +1080,7 @@
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
     </row>
-    <row r="17">
+    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2"/>
       <c r="B17" s="2" t="s">
         <v>7</v>
@@ -997,7 +1115,7 @@
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
     </row>
-    <row r="18">
+    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2"/>
       <c r="B18" s="2" t="s">
         <v>8</v>
@@ -1032,7 +1150,7 @@
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
     </row>
-    <row r="19">
+    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2"/>
       <c r="B19" s="2" t="s">
         <v>9</v>
@@ -1067,7 +1185,7 @@
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
     </row>
-    <row r="20">
+    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2"/>
       <c r="B20" s="2" t="s">
         <v>10</v>
@@ -1102,7 +1220,7 @@
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
     </row>
-    <row r="21">
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2"/>
       <c r="B21" s="2" t="s">
         <v>11</v>
@@ -1137,7 +1255,7 @@
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
     </row>
-    <row r="22">
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2"/>
       <c r="B22" s="2" t="s">
         <v>12</v>
@@ -1172,7 +1290,7 @@
       <c r="N22" s="6"/>
       <c r="O22" s="2"/>
     </row>
-    <row r="23">
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
         <v>13</v>
       </c>
@@ -1180,12 +1298,21 @@
       <c r="C23" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G23" s="9" t="s">
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8" t="s">
         <v>19</v>
       </c>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
       <c r="K23" s="8" t="s">
         <v>20</v>
       </c>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="8"/>
       <c r="O23" s="2"/>
     </row>
   </sheetData>
@@ -1197,6 +1324,12 @@
     <mergeCell ref="G23:J23"/>
     <mergeCell ref="K23:N23"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>